--- a/data/trans_orig/IP09C_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP09C_R-Provincia-trans_orig.xlsx
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9196</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>448</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,83%</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,14%</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>583</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,58%</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -6519,49 +6519,49 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>53,62%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>77,18%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>4158</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>53,62%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>22,87%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>77,01%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>4158</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>7257</t>
-        </is>
-      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>32,02%</t>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12570</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -7427,12 +7427,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -7653,12 +7653,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>449</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7668,12 +7668,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -8109,12 +8109,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>12733</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -8335,12 +8335,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>35878</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>41779</t>
+          <t>43160</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>59183</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -8448,12 +8448,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>28061</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -8561,12 +8561,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>23354</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -8674,12 +8674,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -9140,12 +9140,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9225,12 +9225,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -9479,12 +9479,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9775,12 +9775,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -9818,12 +9818,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>58,72%</t>
         </is>
       </c>
     </row>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10118,12 +10118,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10344,12 +10344,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -10387,12 +10387,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10402,12 +10402,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10422,12 +10422,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10457,12 +10457,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>63,52%</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10570,12 +10570,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10628,12 +10628,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -11295,12 +11295,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11310,12 +11310,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11330,12 +11330,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -11864,12 +11864,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>802</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12807,12 +12807,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13068,12 +13068,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13161,12 +13161,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -13196,12 +13196,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -13715,12 +13715,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -13730,12 +13730,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -13976,12 +13976,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -14054,12 +14054,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -14069,12 +14069,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -14104,12 +14104,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -14137,7 +14137,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>443</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -14182,12 +14182,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -14588,12 +14588,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -14603,12 +14603,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -14623,12 +14623,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -14638,12 +14638,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -14658,12 +14658,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -14673,12 +14673,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -14736,12 +14736,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -14751,12 +14751,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -14771,12 +14771,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -14786,12 +14786,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -14819,7 +14819,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -14884,12 +14884,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -14899,12 +14899,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -14927,12 +14927,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -14942,12 +14942,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -14977,12 +14977,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -14997,12 +14997,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>17378</t>
+          <t>17474</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -15012,12 +15012,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -15496,12 +15496,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -15531,12 +15531,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -15546,12 +15546,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -15566,12 +15566,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -15581,12 +15581,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -15835,12 +15835,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>15004</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -15905,12 +15905,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>18185</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -15920,12 +15920,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -16096,12 +16096,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -16111,12 +16111,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -16131,12 +16131,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -16404,12 +16404,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -16419,12 +16419,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -16439,12 +16439,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>23688</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -16454,12 +16454,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -16474,12 +16474,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -16517,12 +16517,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -16532,12 +16532,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -16552,12 +16552,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -16567,12 +16567,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -16587,12 +16587,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -16630,12 +16630,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -16645,12 +16645,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -16680,12 +16680,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -16700,12 +16700,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -16715,12 +16715,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -16743,12 +16743,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>43768</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -16758,12 +16758,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -16778,12 +16778,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>29455</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>45289</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -16793,12 +16793,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>62877</t>
+          <t>63055</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>83887</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -16828,12 +16828,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -16856,12 +16856,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -16891,12 +16891,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -16906,12 +16906,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -16969,12 +16969,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -17004,12 +17004,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>25007</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -17054,12 +17054,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -17082,12 +17082,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -17097,12 +17097,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -17117,12 +17117,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -17132,12 +17132,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>28019</t>
+          <t>27791</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -17167,12 +17167,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -17588,7 +17588,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -17603,7 +17603,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -17779,7 +17779,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -17809,12 +17809,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -17824,12 +17824,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -17844,12 +17844,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -17859,12 +17859,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -17887,12 +17887,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -17922,12 +17922,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -17937,12 +17937,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -17957,12 +17957,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11964</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -17972,12 +17972,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>78,71%</t>
         </is>
       </c>
     </row>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -18531,7 +18531,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -18870,7 +18870,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -19096,7 +19096,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -19111,7 +19111,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -19439,7 +19439,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -19454,7 +19454,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -19680,7 +19680,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -19723,44 +19723,44 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>65,99%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>65,99%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -19773,12 +19773,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -19906,7 +19906,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>73,26%</t>
         </is>
       </c>
     </row>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -20327,7 +20327,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -20342,12 +20342,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -20357,12 +20357,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -20425,7 +20425,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -20455,12 +20455,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>544</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -20470,12 +20470,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -20538,7 +20538,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -20611,12 +20611,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -20626,12 +20626,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -20681,12 +20681,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -20696,12 +20696,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -20794,12 +20794,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -20809,12 +20809,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -20842,7 +20842,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -20892,7 +20892,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -20907,12 +20907,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>572</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -20922,12 +20922,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -20990,7 +20990,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -21025,7 +21025,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -22108,7 +22108,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -22123,12 +22123,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -22138,12 +22138,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -22158,12 +22158,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -22173,12 +22173,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -22319,7 +22319,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -22369,7 +22369,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -22427,12 +22427,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -22442,12 +22442,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -22497,12 +22497,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -22512,12 +22512,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -22580,7 +22580,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -22595,7 +22595,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -22653,12 +22653,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -22668,12 +22668,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -22688,12 +22688,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -22703,12 +22703,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -22723,12 +22723,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -22738,12 +22738,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>65,54%</t>
         </is>
       </c>
     </row>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -23031,12 +23031,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -23046,12 +23046,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -23066,12 +23066,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -23081,12 +23081,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -23129,7 +23129,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -23227,7 +23227,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -23335,12 +23335,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -23350,12 +23350,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -23370,12 +23370,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -23385,12 +23385,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -23405,12 +23405,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -23420,12 +23420,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -23488,7 +23488,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -23503,7 +23503,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -23601,7 +23601,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -23651,7 +23651,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -23679,7 +23679,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -23744,12 +23744,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -23759,12 +23759,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -23904,12 +23904,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -23919,12 +23919,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -23939,12 +23939,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -23954,12 +23954,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -23974,12 +23974,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -23989,12 +23989,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,35%</t>
         </is>
       </c>
     </row>
@@ -24170,7 +24170,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -24220,7 +24220,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -24248,7 +24248,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -24278,12 +24278,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>520</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -24293,12 +24293,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -24313,12 +24313,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -24328,12 +24328,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -24356,12 +24356,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -24371,12 +24371,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -24426,12 +24426,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -24441,12 +24441,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -24474,7 +24474,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -24489,7 +24489,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -24559,7 +24559,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -24812,12 +24812,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -24827,12 +24827,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -24847,12 +24847,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -24862,12 +24862,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -24882,12 +24882,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -24897,12 +24897,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -24925,12 +24925,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>515</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -24940,12 +24940,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -24965,7 +24965,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -24980,7 +24980,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -24995,12 +24995,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -25010,12 +25010,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -25038,12 +25038,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -25073,12 +25073,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -25088,12 +25088,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -25108,12 +25108,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -25123,12 +25123,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -25166,12 +25166,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -25186,12 +25186,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -25201,12 +25201,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -25221,12 +25221,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -25236,12 +25236,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -25264,12 +25264,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -25279,12 +25279,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -25299,12 +25299,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -25314,12 +25314,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -25334,12 +25334,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -25349,12 +25349,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -25377,12 +25377,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -25392,12 +25392,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -25412,12 +25412,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -25427,12 +25427,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -25447,12 +25447,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -25467,7 +25467,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -25525,12 +25525,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -25560,12 +25560,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -25575,12 +25575,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
